--- a/target/classes/com/mycompany/ocxrst/BASES/TIPOMONEDA.xlsx
+++ b/target/classes/com/mycompany/ocxrst/BASES/TIPOMONEDA.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OCXRST\OrdendeComprasRST\src\main\java\com\mycompany\ocxrst\BASES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E190922A-1587-47AB-862C-4F3ABA0B70CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B8A475-D4B0-4C3E-87D5-9B14D2416E32}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2870" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{AE138996-7349-4012-AA97-938975CD6540}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AE138996-7349-4012-AA97-938975CD6540}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -23,12 +23,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>moneda</t>
   </si>
@@ -69,13 +64,19 @@
   </si>
   <si>
     <t>** Selecciona una opción **</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>Peso Dólar Canadiense</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -440,15 +441,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE7502A-D30C-4A1F-B5B3-31EE5262FE39}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="101.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="101.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -459,7 +460,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -470,7 +471,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -481,7 +482,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -489,12 +490,20 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
